--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122232618</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562689</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7040030</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1010,6 +1010,765 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122425175</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562654</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039885</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122425101</v>
+      </c>
+      <c r="B6" t="n">
+        <v>55974</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562669</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039963</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122425154</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562640</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122425134</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562671</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122425106</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562664</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039963</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122425163</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562631</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039921</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122425212</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Håsjöån, Håsjöån, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039899</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425175</v>
+        <v>122425101</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>55974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1029,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562654</v>
+        <v>562669</v>
       </c>
       <c r="R5" t="n">
-        <v>7039885</v>
+        <v>7039963</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,9 +1091,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,22 +1118,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425101</v>
+        <v>122425212</v>
       </c>
       <c r="B6" t="n">
-        <v>55974</v>
+        <v>79727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1146,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562669</v>
+        <v>562627</v>
       </c>
       <c r="R6" t="n">
-        <v>7039963</v>
+        <v>7039899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425154</v>
+        <v>122425175</v>
       </c>
       <c r="B7" t="n">
         <v>79727</v>
@@ -1272,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562640</v>
+        <v>562654</v>
       </c>
       <c r="R7" t="n">
-        <v>7039916</v>
+        <v>7039885</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1334,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425134</v>
+        <v>122425154</v>
       </c>
       <c r="B8" t="n">
         <v>79727</v>
@@ -1374,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562671</v>
+        <v>562640</v>
       </c>
       <c r="R8" t="n">
-        <v>7039947</v>
+        <v>7039916</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,7 +1446,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425106</v>
+        <v>122425163</v>
       </c>
       <c r="B9" t="n">
         <v>79727</v>
@@ -1476,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562664</v>
+        <v>562631</v>
       </c>
       <c r="R9" t="n">
-        <v>7039963</v>
+        <v>7039921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425163</v>
+        <v>122425134</v>
       </c>
       <c r="B10" t="n">
         <v>79727</v>
@@ -1588,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562631</v>
+        <v>562671</v>
       </c>
       <c r="R10" t="n">
-        <v>7039921</v>
+        <v>7039947</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,19 +1631,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,19 +1648,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425212</v>
+        <v>122425106</v>
       </c>
       <c r="B11" t="n">
         <v>79727</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562627</v>
+        <v>562664</v>
       </c>
       <c r="R11" t="n">
-        <v>7039899</v>
+        <v>7039963</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>122425101</v>
       </c>
       <c r="B5" t="n">
-        <v>55974</v>
+        <v>55979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425212</v>
+        <v>122425175</v>
       </c>
       <c r="B6" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562627</v>
+        <v>562654</v>
       </c>
       <c r="R6" t="n">
-        <v>7039899</v>
+        <v>7039885</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,19 +1203,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425175</v>
+        <v>122425134</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562654</v>
+        <v>562671</v>
       </c>
       <c r="R7" t="n">
-        <v>7039885</v>
+        <v>7039947</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1344,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425154</v>
+        <v>122425163</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562640</v>
+        <v>562631</v>
       </c>
       <c r="R8" t="n">
-        <v>7039916</v>
+        <v>7039921</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,9 +1407,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,22 +1434,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425163</v>
+        <v>122425212</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562631</v>
+        <v>562627</v>
       </c>
       <c r="R9" t="n">
-        <v>7039921</v>
+        <v>7039899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,22 +1546,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425134</v>
+        <v>122425154</v>
       </c>
       <c r="B10" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562671</v>
+        <v>562640</v>
       </c>
       <c r="R10" t="n">
-        <v>7039947</v>
+        <v>7039916</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,7 +1663,7 @@
         <v>122425106</v>
       </c>
       <c r="B11" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425101</v>
+        <v>122425212</v>
       </c>
       <c r="B5" t="n">
-        <v>55979</v>
+        <v>79732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,39 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562669</v>
+        <v>562627</v>
       </c>
       <c r="R5" t="n">
-        <v>7039963</v>
+        <v>7039899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425175</v>
+        <v>122425154</v>
       </c>
       <c r="B6" t="n">
         <v>79732</v>
@@ -1170,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562654</v>
+        <v>562640</v>
       </c>
       <c r="R6" t="n">
-        <v>7039885</v>
+        <v>7039916</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1232,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425134</v>
+        <v>122425175</v>
       </c>
       <c r="B7" t="n">
         <v>79732</v>
@@ -1272,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562671</v>
+        <v>562654</v>
       </c>
       <c r="R7" t="n">
-        <v>7039947</v>
+        <v>7039885</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1334,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425163</v>
+        <v>122425134</v>
       </c>
       <c r="B8" t="n">
         <v>79732</v>
@@ -1374,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562631</v>
+        <v>562671</v>
       </c>
       <c r="R8" t="n">
-        <v>7039921</v>
+        <v>7039947</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,19 +1402,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,19 +1419,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425212</v>
+        <v>122425106</v>
       </c>
       <c r="B9" t="n">
         <v>79732</v>
@@ -1486,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562627</v>
+        <v>562664</v>
       </c>
       <c r="R9" t="n">
-        <v>7039899</v>
+        <v>7039963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1506,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1516,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,19 +1531,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425154</v>
+        <v>122425163</v>
       </c>
       <c r="B10" t="n">
         <v>79732</v>
@@ -1598,13 +1583,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562640</v>
+        <v>562631</v>
       </c>
       <c r="R10" t="n">
-        <v>7039916</v>
+        <v>7039921</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,9 +1616,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1643,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425106</v>
+        <v>122425101</v>
       </c>
       <c r="B11" t="n">
-        <v>79732</v>
+        <v>55979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,31 +1671,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562664</v>
+        <v>562669</v>
       </c>
       <c r="R11" t="n">
         <v>7039963</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,11 +924,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425212</v>
+        <v>122425163</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,11 +1026,6 @@
       <c r="E5" t="n">
         <v>6458</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1053,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562627</v>
+        <v>562631</v>
       </c>
       <c r="R5" t="n">
-        <v>7039899</v>
+        <v>7039921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1103,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425154</v>
+        <v>122425175</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,11 +1133,6 @@
       <c r="E6" t="n">
         <v>6458</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1165,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562640</v>
+        <v>562654</v>
       </c>
       <c r="R6" t="n">
-        <v>7039916</v>
+        <v>7039885</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1227,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425175</v>
+        <v>122425134</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,11 +1230,6 @@
       <c r="E7" t="n">
         <v>6458</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1267,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562654</v>
+        <v>562671</v>
       </c>
       <c r="R7" t="n">
-        <v>7039885</v>
+        <v>7039947</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1329,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425134</v>
+        <v>122425101</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
+        <v>55979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,37 +1325,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>206004</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562671</v>
+        <v>562669</v>
       </c>
       <c r="R8" t="n">
-        <v>7039947</v>
+        <v>7039963</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,9 +1382,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,12 +1409,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1434,7 +1424,7 @@
         <v>122425106</v>
       </c>
       <c r="B9" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,11 +1438,6 @@
       </c>
       <c r="E9" t="n">
         <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1543,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425163</v>
+        <v>122425212</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,11 +1546,6 @@
       <c r="E10" t="n">
         <v>6458</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1583,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562631</v>
+        <v>562627</v>
       </c>
       <c r="R10" t="n">
-        <v>7039921</v>
+        <v>7039899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1598,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1628,7 +1608,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,22 +1623,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425101</v>
+        <v>122425154</v>
       </c>
       <c r="B11" t="n">
-        <v>55979</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,42 +1651,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562669</v>
+        <v>562640</v>
       </c>
       <c r="R11" t="n">
-        <v>7039963</v>
+        <v>7039916</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,19 +1703,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1720,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,6 +924,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425163</v>
+        <v>122425154</v>
       </c>
       <c r="B5" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,6 +1031,11 @@
       <c r="E5" t="n">
         <v>6458</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1043,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562631</v>
+        <v>562640</v>
       </c>
       <c r="R5" t="n">
-        <v>7039921</v>
+        <v>7039916</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,19 +1086,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>122425175</v>
       </c>
       <c r="B6" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,6 +1132,11 @@
       </c>
       <c r="E6" t="n">
         <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1212,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425134</v>
+        <v>122425101</v>
       </c>
       <c r="B7" t="n">
-        <v>79733</v>
+        <v>55983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,32 +1233,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>206004</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562671</v>
+        <v>562669</v>
       </c>
       <c r="R7" t="n">
-        <v>7039947</v>
+        <v>7039963</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,9 +1295,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,22 +1322,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425101</v>
+        <v>122425134</v>
       </c>
       <c r="B8" t="n">
-        <v>55979</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,37 +1350,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562669</v>
+        <v>562671</v>
       </c>
       <c r="R8" t="n">
-        <v>7039963</v>
+        <v>7039947</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,19 +1407,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,12 +1424,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1424,7 +1439,7 @@
         <v>122425106</v>
       </c>
       <c r="B9" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,6 +1453,11 @@
       </c>
       <c r="E9" t="n">
         <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1531,7 +1551,7 @@
         <v>122425212</v>
       </c>
       <c r="B10" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,6 +1565,11 @@
       </c>
       <c r="E10" t="n">
         <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1635,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425154</v>
+        <v>122425163</v>
       </c>
       <c r="B11" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,6 +1678,11 @@
       <c r="E11" t="n">
         <v>6458</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1670,13 +1700,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562640</v>
+        <v>562631</v>
       </c>
       <c r="R11" t="n">
-        <v>7039916</v>
+        <v>7039921</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,9 +1733,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425154</v>
+        <v>122425212</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562640</v>
+        <v>562627</v>
       </c>
       <c r="R5" t="n">
-        <v>7039916</v>
+        <v>7039899</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,9 +1086,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,19 +1113,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425175</v>
+        <v>122425106</v>
       </c>
       <c r="B6" t="n">
         <v>79737</v>
@@ -1155,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562654</v>
+        <v>562664</v>
       </c>
       <c r="R6" t="n">
-        <v>7039885</v>
+        <v>7039963</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,9 +1198,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425101</v>
+        <v>122425154</v>
       </c>
       <c r="B7" t="n">
-        <v>55983</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,42 +1253,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562669</v>
+        <v>562640</v>
       </c>
       <c r="R7" t="n">
-        <v>7039963</v>
+        <v>7039916</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,19 +1310,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,19 +1327,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425134</v>
+        <v>122425175</v>
       </c>
       <c r="B8" t="n">
         <v>79737</v>
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562671</v>
+        <v>562654</v>
       </c>
       <c r="R8" t="n">
-        <v>7039947</v>
+        <v>7039885</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425106</v>
+        <v>122425101</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,31 +1457,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562664</v>
+        <v>562669</v>
       </c>
       <c r="R9" t="n">
         <v>7039963</v>
@@ -1511,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,19 +1546,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425212</v>
+        <v>122425163</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1588,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562627</v>
+        <v>562631</v>
       </c>
       <c r="R10" t="n">
-        <v>7039899</v>
+        <v>7039921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,19 +1658,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425163</v>
+        <v>122425134</v>
       </c>
       <c r="B11" t="n">
         <v>79737</v>
@@ -1700,13 +1710,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562631</v>
+        <v>562671</v>
       </c>
       <c r="R11" t="n">
-        <v>7039921</v>
+        <v>7039947</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,19 +1743,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425212</v>
+        <v>122425154</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562627</v>
+        <v>562640</v>
       </c>
       <c r="R5" t="n">
-        <v>7039899</v>
+        <v>7039916</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,19 +1086,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1103,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425106</v>
+        <v>122425101</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1131,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562664</v>
+        <v>562669</v>
       </c>
       <c r="R6" t="n">
         <v>7039963</v>
@@ -1200,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,19 +1220,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425154</v>
+        <v>122425134</v>
       </c>
       <c r="B7" t="n">
         <v>79737</v>
@@ -1277,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562640</v>
+        <v>562671</v>
       </c>
       <c r="R7" t="n">
-        <v>7039916</v>
+        <v>7039947</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1441,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425101</v>
+        <v>122425163</v>
       </c>
       <c r="B9" t="n">
-        <v>55983</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,39 +1452,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562669</v>
+        <v>562631</v>
       </c>
       <c r="R9" t="n">
-        <v>7039963</v>
+        <v>7039921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1531,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,19 +1536,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425163</v>
+        <v>122425106</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1598,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562631</v>
+        <v>562664</v>
       </c>
       <c r="R10" t="n">
-        <v>7039921</v>
+        <v>7039963</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425134</v>
+        <v>122425212</v>
       </c>
       <c r="B11" t="n">
         <v>79737</v>
@@ -1710,13 +1700,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562671</v>
+        <v>562627</v>
       </c>
       <c r="R11" t="n">
-        <v>7039947</v>
+        <v>7039899</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,9 +1733,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>122232618</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425154</v>
+        <v>122425212</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562640</v>
+        <v>562627</v>
       </c>
       <c r="R5" t="n">
-        <v>7039916</v>
+        <v>7039899</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,9 +1086,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425101</v>
+        <v>122425106</v>
       </c>
       <c r="B6" t="n">
-        <v>55983</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,36 +1141,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562669</v>
+        <v>562664</v>
       </c>
       <c r="R6" t="n">
         <v>7039963</v>
@@ -1195,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,19 +1225,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425134</v>
+        <v>122425154</v>
       </c>
       <c r="B7" t="n">
         <v>79737</v>
@@ -1272,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562671</v>
+        <v>562640</v>
       </c>
       <c r="R7" t="n">
-        <v>7039947</v>
+        <v>7039916</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1334,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425175</v>
+        <v>122425163</v>
       </c>
       <c r="B8" t="n">
         <v>79737</v>
@@ -1374,13 +1379,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562654</v>
+        <v>562631</v>
       </c>
       <c r="R8" t="n">
-        <v>7039885</v>
+        <v>7039921</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,9 +1412,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,22 +1439,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425163</v>
+        <v>122425101</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,34 +1467,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562631</v>
+        <v>562669</v>
       </c>
       <c r="R9" t="n">
-        <v>7039921</v>
+        <v>7039963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,19 +1556,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425106</v>
+        <v>122425175</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1588,13 +1608,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562664</v>
+        <v>562654</v>
       </c>
       <c r="R10" t="n">
-        <v>7039963</v>
+        <v>7039885</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,19 +1641,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,19 +1658,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425212</v>
+        <v>122425134</v>
       </c>
       <c r="B11" t="n">
         <v>79737</v>
@@ -1700,13 +1710,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562627</v>
+        <v>562671</v>
       </c>
       <c r="R11" t="n">
-        <v>7039899</v>
+        <v>7039947</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,19 +1743,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425212</v>
+        <v>122425163</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562627</v>
+        <v>562631</v>
       </c>
       <c r="R5" t="n">
-        <v>7039899</v>
+        <v>7039921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,19 +1113,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425106</v>
+        <v>122425175</v>
       </c>
       <c r="B6" t="n">
         <v>79737</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562664</v>
+        <v>562654</v>
       </c>
       <c r="R6" t="n">
-        <v>7039963</v>
+        <v>7039885</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,19 +1198,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,12 +1215,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1339,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425163</v>
+        <v>122425134</v>
       </c>
       <c r="B8" t="n">
         <v>79737</v>
@@ -1379,13 +1369,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562631</v>
+        <v>562671</v>
       </c>
       <c r="R8" t="n">
-        <v>7039921</v>
+        <v>7039947</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,19 +1402,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,22 +1419,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425101</v>
+        <v>122425106</v>
       </c>
       <c r="B9" t="n">
-        <v>55983</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,36 +1447,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562669</v>
+        <v>562664</v>
       </c>
       <c r="R9" t="n">
         <v>7039963</v>
@@ -1531,7 +1506,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1516,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,22 +1531,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425175</v>
+        <v>122425101</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,37 +1559,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562654</v>
+        <v>562669</v>
       </c>
       <c r="R10" t="n">
-        <v>7039885</v>
+        <v>7039963</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,9 +1621,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,19 +1648,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425134</v>
+        <v>122425212</v>
       </c>
       <c r="B11" t="n">
         <v>79737</v>
@@ -1710,13 +1700,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562671</v>
+        <v>562627</v>
       </c>
       <c r="R11" t="n">
-        <v>7039947</v>
+        <v>7039899</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,9 +1733,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>122425163</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>122425175</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>122425154</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425134</v>
+        <v>122425101</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
+        <v>55984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,37 +1345,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562671</v>
+        <v>562669</v>
       </c>
       <c r="R8" t="n">
-        <v>7039947</v>
+        <v>7039963</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,9 +1407,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,22 +1434,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425106</v>
+        <v>122425134</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,13 +1486,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562664</v>
+        <v>562671</v>
       </c>
       <c r="R9" t="n">
-        <v>7039963</v>
+        <v>7039947</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,19 +1519,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,22 +1536,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425101</v>
+        <v>122425106</v>
       </c>
       <c r="B10" t="n">
-        <v>55983</v>
+        <v>79738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,36 +1564,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562669</v>
+        <v>562664</v>
       </c>
       <c r="R10" t="n">
         <v>7039963</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,12 +1648,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
         <v>122425212</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425163</v>
+        <v>122425212</v>
       </c>
       <c r="B5" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562631</v>
+        <v>562627</v>
       </c>
       <c r="R5" t="n">
-        <v>7039921</v>
+        <v>7039899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1113,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122425175</v>
+        <v>122425134</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562654</v>
+        <v>562671</v>
       </c>
       <c r="R6" t="n">
-        <v>7039885</v>
+        <v>7039947</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425154</v>
+        <v>122425175</v>
       </c>
       <c r="B7" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562640</v>
+        <v>562654</v>
       </c>
       <c r="R7" t="n">
-        <v>7039916</v>
+        <v>7039885</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425101</v>
+        <v>122425154</v>
       </c>
       <c r="B8" t="n">
-        <v>55984</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,42 +1345,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562669</v>
+        <v>562640</v>
       </c>
       <c r="R8" t="n">
-        <v>7039963</v>
+        <v>7039916</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,19 +1402,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,22 +1419,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425134</v>
+        <v>122425106</v>
       </c>
       <c r="B9" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,13 +1471,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562671</v>
+        <v>562664</v>
       </c>
       <c r="R9" t="n">
-        <v>7039947</v>
+        <v>7039963</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,9 +1504,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,22 +1531,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425106</v>
+        <v>122425101</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>55984</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,31 +1559,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562664</v>
+        <v>562669</v>
       </c>
       <c r="R10" t="n">
         <v>7039963</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1648,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425212</v>
+        <v>122425163</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562627</v>
+        <v>562631</v>
       </c>
       <c r="R11" t="n">
-        <v>7039899</v>
+        <v>7039921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 45084-2022 artfynd.xlsx
+++ b/artfynd/A 45084-2022 artfynd.xlsx
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122425212</v>
+        <v>122425106</v>
       </c>
       <c r="B5" t="n">
         <v>79741</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562627</v>
+        <v>562664</v>
       </c>
       <c r="R5" t="n">
-        <v>7039899</v>
+        <v>7039963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,12 +1113,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122425175</v>
+        <v>122425212</v>
       </c>
       <c r="B7" t="n">
         <v>79741</v>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562654</v>
+        <v>562627</v>
       </c>
       <c r="R7" t="n">
-        <v>7039885</v>
+        <v>7039899</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,9 +1300,19 @@
           <t>2025-02-02</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1327,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122425154</v>
+        <v>122425175</v>
       </c>
       <c r="B8" t="n">
         <v>79741</v>
@@ -1369,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562640</v>
+        <v>562654</v>
       </c>
       <c r="R8" t="n">
-        <v>7039916</v>
+        <v>7039885</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1431,7 +1441,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122425106</v>
+        <v>122425163</v>
       </c>
       <c r="B9" t="n">
         <v>79741</v>
@@ -1471,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562664</v>
+        <v>562631</v>
       </c>
       <c r="R9" t="n">
-        <v>7039963</v>
+        <v>7039921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1516,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122425101</v>
+        <v>122425154</v>
       </c>
       <c r="B10" t="n">
-        <v>55984</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,42 +1569,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562669</v>
+        <v>562640</v>
       </c>
       <c r="R10" t="n">
-        <v>7039963</v>
+        <v>7039916</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,19 +1626,9 @@
           <t>2025-02-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1643,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122425163</v>
+        <v>122425101</v>
       </c>
       <c r="B11" t="n">
-        <v>79741</v>
+        <v>55984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,34 +1671,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Håsjöån, Håsjöån, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562631</v>
+        <v>562669</v>
       </c>
       <c r="R11" t="n">
-        <v>7039921</v>
+        <v>7039963</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,12 +1760,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
